--- a/data/nzd0065/nzd0065.xlsx
+++ b/data/nzd0065/nzd0065.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC214"/>
+  <dimension ref="A1:AC215"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20289,6 +20289,99 @@
         </is>
       </c>
     </row>
+    <row r="215">
+      <c r="A215" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:17:07+00:00</t>
+        </is>
+      </c>
+      <c r="B215" t="n">
+        <v>424.85</v>
+      </c>
+      <c r="C215" t="n">
+        <v>397.11</v>
+      </c>
+      <c r="D215" t="n">
+        <v>385.77</v>
+      </c>
+      <c r="E215" t="n">
+        <v>373.27</v>
+      </c>
+      <c r="F215" t="n">
+        <v>370.05</v>
+      </c>
+      <c r="G215" t="n">
+        <v>364.34</v>
+      </c>
+      <c r="H215" t="n">
+        <v>363.03</v>
+      </c>
+      <c r="I215" t="n">
+        <v>356.22</v>
+      </c>
+      <c r="J215" t="n">
+        <v>366.98</v>
+      </c>
+      <c r="K215" t="n">
+        <v>370.42</v>
+      </c>
+      <c r="L215" t="n">
+        <v>344.81</v>
+      </c>
+      <c r="M215" t="n">
+        <v>352.75</v>
+      </c>
+      <c r="N215" t="n">
+        <v>343.52</v>
+      </c>
+      <c r="O215" t="n">
+        <v>342.88</v>
+      </c>
+      <c r="P215" t="n">
+        <v>344.7</v>
+      </c>
+      <c r="Q215" t="n">
+        <v>339.15</v>
+      </c>
+      <c r="R215" t="n">
+        <v>331.67</v>
+      </c>
+      <c r="S215" t="n">
+        <v>343.96</v>
+      </c>
+      <c r="T215" t="n">
+        <v>339.84</v>
+      </c>
+      <c r="U215" t="n">
+        <v>338.45</v>
+      </c>
+      <c r="V215" t="n">
+        <v>336.31</v>
+      </c>
+      <c r="W215" t="n">
+        <v>336.85</v>
+      </c>
+      <c r="X215" t="n">
+        <v>344.89</v>
+      </c>
+      <c r="Y215" t="n">
+        <v>351.19</v>
+      </c>
+      <c r="Z215" t="n">
+        <v>340.67</v>
+      </c>
+      <c r="AA215" t="n">
+        <v>333.7</v>
+      </c>
+      <c r="AB215" t="n">
+        <v>351.56</v>
+      </c>
+      <c r="AC215" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -20300,7 +20393,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B218"/>
+  <dimension ref="A1:B219"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22483,6 +22576,16 @@
       </c>
       <c r="B218" t="n">
         <v>0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B219" t="n">
+        <v>-0.71</v>
       </c>
     </row>
   </sheetData>
@@ -22651,28 +22754,28 @@
         <v>0.0257</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.8645591598677195</v>
+        <v>-0.8268173668510771</v>
       </c>
       <c r="J2" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K2" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08665800889308239</v>
+        <v>0.07926167596613221</v>
       </c>
       <c r="M2" t="n">
-        <v>15.76291437192226</v>
+        <v>15.88362196899181</v>
       </c>
       <c r="N2" t="n">
-        <v>482.7285445734694</v>
+        <v>489.1600434547032</v>
       </c>
       <c r="O2" t="n">
-        <v>21.97108428306326</v>
+        <v>22.1169627990532</v>
       </c>
       <c r="P2" t="n">
-        <v>404.8551138534483</v>
+        <v>404.4775135694399</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -22729,28 +22832,28 @@
         <v>0.0356</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5153402435936807</v>
+        <v>-0.4914582342201636</v>
       </c>
       <c r="J3" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K3" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06680014255271405</v>
+        <v>0.06081625501557697</v>
       </c>
       <c r="M3" t="n">
-        <v>11.5084846840155</v>
+        <v>11.56009346625804</v>
       </c>
       <c r="N3" t="n">
-        <v>228.6656385830702</v>
+        <v>231.0990526356215</v>
       </c>
       <c r="O3" t="n">
-        <v>15.12169430265902</v>
+        <v>15.20194239679988</v>
       </c>
       <c r="P3" t="n">
-        <v>383.4597742194393</v>
+        <v>383.2223243004132</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -22807,28 +22910,28 @@
         <v>0.0412</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1891989893279764</v>
+        <v>-0.1746914447520918</v>
       </c>
       <c r="J4" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K4" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01424034838416122</v>
+        <v>0.0121842151317072</v>
       </c>
       <c r="M4" t="n">
-        <v>9.730856488220079</v>
+        <v>9.753631235584772</v>
       </c>
       <c r="N4" t="n">
-        <v>152.219247989604</v>
+        <v>152.7920883707046</v>
       </c>
       <c r="O4" t="n">
-        <v>12.33771648197526</v>
+        <v>12.36090969025761</v>
       </c>
       <c r="P4" t="n">
-        <v>374.1688123512546</v>
+        <v>374.0244698183045</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -22885,28 +22988,28 @@
         <v>0.0423</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.002893991096157725</v>
+        <v>0.002564785287642266</v>
       </c>
       <c r="J5" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K5" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L5" t="n">
-        <v>3.583394073247703e-06</v>
+        <v>2.839216602934513e-06</v>
       </c>
       <c r="M5" t="n">
-        <v>9.767900641636455</v>
+        <v>9.746302517506674</v>
       </c>
       <c r="N5" t="n">
-        <v>143.575315057384</v>
+        <v>143.0808327227401</v>
       </c>
       <c r="O5" t="n">
-        <v>11.98229172810377</v>
+        <v>11.96164005154561</v>
       </c>
       <c r="P5" t="n">
-        <v>367.0818394169555</v>
+        <v>367.027527427361</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -22963,28 +23066,28 @@
         <v>0.0459</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.03910265227984999</v>
+        <v>-0.03467572894923878</v>
       </c>
       <c r="J6" t="n">
+        <v>214</v>
+      </c>
+      <c r="K6" t="n">
         <v>213</v>
       </c>
-      <c r="K6" t="n">
-        <v>212</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.0006649876109268149</v>
+        <v>0.0005277819815435736</v>
       </c>
       <c r="M6" t="n">
-        <v>9.602130031175367</v>
+        <v>9.576315476068089</v>
       </c>
       <c r="N6" t="n">
-        <v>140.8928470236337</v>
+        <v>140.3522997897001</v>
       </c>
       <c r="O6" t="n">
-        <v>11.86982927525218</v>
+        <v>11.84703759552151</v>
       </c>
       <c r="P6" t="n">
-        <v>365.9842251332005</v>
+        <v>365.9400677140811</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -23041,28 +23144,28 @@
         <v>0.0435</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.07954969555132714</v>
+        <v>-0.07705316900180027</v>
       </c>
       <c r="J7" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K7" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L7" t="n">
-        <v>0.003642857368297836</v>
+        <v>0.003451281904765069</v>
       </c>
       <c r="M7" t="n">
-        <v>7.895590109437227</v>
+        <v>7.871015814062355</v>
       </c>
       <c r="N7" t="n">
-        <v>105.6585105760551</v>
+        <v>105.2031354435851</v>
       </c>
       <c r="O7" t="n">
-        <v>10.27903257004545</v>
+        <v>10.25685797130803</v>
       </c>
       <c r="P7" t="n">
-        <v>363.5856647605222</v>
+        <v>363.5606914908464</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -23119,28 +23222,28 @@
         <v>0.041</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01732743057497598</v>
+        <v>0.01983018385054353</v>
       </c>
       <c r="J8" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K8" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L8" t="n">
-        <v>0.000234052207219837</v>
+        <v>0.0003094279451482107</v>
       </c>
       <c r="M8" t="n">
-        <v>7.072036368093356</v>
+        <v>7.054590494117666</v>
       </c>
       <c r="N8" t="n">
-        <v>78.29039851545312</v>
+        <v>77.96310332850479</v>
       </c>
       <c r="O8" t="n">
-        <v>8.848186170930918</v>
+        <v>8.829671756554985</v>
       </c>
       <c r="P8" t="n">
-        <v>359.6730281301284</v>
+        <v>359.6479925732286</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -23197,28 +23300,28 @@
         <v>0.0357</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2706789903082319</v>
+        <v>-0.2661141596553411</v>
       </c>
       <c r="J9" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K9" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03660561549284957</v>
+        <v>0.03572763599091744</v>
       </c>
       <c r="M9" t="n">
-        <v>9.064239883532577</v>
+        <v>9.045723851182744</v>
       </c>
       <c r="N9" t="n">
-        <v>117.7118165786675</v>
+        <v>117.2899982061304</v>
       </c>
       <c r="O9" t="n">
-        <v>10.84950766526608</v>
+        <v>10.83005070191873</v>
       </c>
       <c r="P9" t="n">
-        <v>358.1828110375238</v>
+        <v>358.1371480955691</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -23275,28 +23378,28 @@
         <v>0.0255</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1902652096535137</v>
+        <v>-0.1685233997598322</v>
       </c>
       <c r="J10" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K10" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01129425734119494</v>
+        <v>0.008837593727678783</v>
       </c>
       <c r="M10" t="n">
-        <v>10.89902886001075</v>
+        <v>10.96458881368194</v>
       </c>
       <c r="N10" t="n">
-        <v>193.4562277252201</v>
+        <v>195.4613013509803</v>
       </c>
       <c r="O10" t="n">
-        <v>13.90885429232832</v>
+        <v>13.98074752475633</v>
       </c>
       <c r="P10" t="n">
-        <v>346.9421503218221</v>
+        <v>346.7246625158868</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -23353,28 +23456,28 @@
         <v>0.0232</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3196494181922851</v>
+        <v>-0.2888338325029592</v>
       </c>
       <c r="J11" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K11" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0251141042250278</v>
+        <v>0.02031890963791227</v>
       </c>
       <c r="M11" t="n">
-        <v>12.42809760917491</v>
+        <v>12.54770671353088</v>
       </c>
       <c r="N11" t="n">
-        <v>242.1243684592201</v>
+        <v>246.8368671807528</v>
       </c>
       <c r="O11" t="n">
-        <v>15.56034602633309</v>
+        <v>15.71104284192341</v>
       </c>
       <c r="P11" t="n">
-        <v>343.3491372736301</v>
+        <v>343.0408826180629</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -23431,28 +23534,28 @@
         <v>0.031</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.3522028456352844</v>
+        <v>-0.3448552428914346</v>
       </c>
       <c r="J12" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K12" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L12" t="n">
-        <v>0.04737229724855452</v>
+        <v>0.04584241744987982</v>
       </c>
       <c r="M12" t="n">
-        <v>10.0925174676873</v>
+        <v>10.0907507449108</v>
       </c>
       <c r="N12" t="n">
-        <v>152.2786617681897</v>
+        <v>151.8993214558444</v>
       </c>
       <c r="O12" t="n">
-        <v>12.34012405805508</v>
+        <v>12.32474427547462</v>
       </c>
       <c r="P12" t="n">
-        <v>345.7404129119759</v>
+        <v>345.6669133271917</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -23509,28 +23612,28 @@
         <v>0.036</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2807925614954142</v>
+        <v>-0.2671672683870558</v>
       </c>
       <c r="J13" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K13" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L13" t="n">
-        <v>0.02935477813348009</v>
+        <v>0.02672018112986041</v>
       </c>
       <c r="M13" t="n">
-        <v>9.938325858838352</v>
+        <v>9.972240126281546</v>
       </c>
       <c r="N13" t="n">
-        <v>159.1503087347202</v>
+        <v>159.5491130258649</v>
       </c>
       <c r="O13" t="n">
-        <v>12.61547893402071</v>
+        <v>12.6312751939725</v>
       </c>
       <c r="P13" t="n">
-        <v>344.5120490077702</v>
+        <v>344.3757523922698</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -23587,28 +23690,28 @@
         <v>0.0414</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.309816698902268</v>
+        <v>-0.2986938417975329</v>
       </c>
       <c r="J14" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K14" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L14" t="n">
-        <v>0.03250851965806301</v>
+        <v>0.03044892369422725</v>
       </c>
       <c r="M14" t="n">
-        <v>10.63704925864408</v>
+        <v>10.64320895688575</v>
       </c>
       <c r="N14" t="n">
-        <v>174.3870253695629</v>
+        <v>174.3335034973459</v>
       </c>
       <c r="O14" t="n">
-        <v>13.20556796845796</v>
+        <v>13.2035413241049</v>
       </c>
       <c r="P14" t="n">
-        <v>338.9592191495425</v>
+        <v>338.8479549172054</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -23665,28 +23768,28 @@
         <v>0.042</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3346987687197234</v>
+        <v>-0.3212595948569906</v>
       </c>
       <c r="J15" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K15" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L15" t="n">
-        <v>0.03206456638912292</v>
+        <v>0.02974367212700291</v>
       </c>
       <c r="M15" t="n">
-        <v>11.7105775494981</v>
+        <v>11.70949581744113</v>
       </c>
       <c r="N15" t="n">
-        <v>207.0769932808031</v>
+        <v>207.217355825719</v>
       </c>
       <c r="O15" t="n">
-        <v>14.39017002265099</v>
+        <v>14.39504622520258</v>
       </c>
       <c r="P15" t="n">
-        <v>336.3356330765282</v>
+        <v>336.2007295207246</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -23743,28 +23846,28 @@
         <v>0.0418</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3318566171133502</v>
+        <v>-0.3133482410937986</v>
       </c>
       <c r="J16" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K16" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L16" t="n">
-        <v>0.02787099070821708</v>
+        <v>0.02494298885408908</v>
       </c>
       <c r="M16" t="n">
-        <v>12.64418558148904</v>
+        <v>12.6620397508207</v>
       </c>
       <c r="N16" t="n">
-        <v>236.0917420887939</v>
+        <v>237.107371243429</v>
       </c>
       <c r="O16" t="n">
-        <v>15.36527715626353</v>
+        <v>15.3982911793299</v>
       </c>
       <c r="P16" t="n">
-        <v>332.2308160378922</v>
+        <v>332.0452278372112</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -23821,28 +23924,28 @@
         <v>0.0382</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.4629464809762934</v>
+        <v>-0.453623192183824</v>
       </c>
       <c r="J17" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K17" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L17" t="n">
-        <v>0.09811147172997503</v>
+        <v>0.09504334948697379</v>
       </c>
       <c r="M17" t="n">
-        <v>8.524540498074607</v>
+        <v>8.524579115198328</v>
       </c>
       <c r="N17" t="n">
-        <v>120.1720253771229</v>
+        <v>120.1320816386303</v>
       </c>
       <c r="O17" t="n">
-        <v>10.96230018641722</v>
+        <v>10.96047816651401</v>
       </c>
       <c r="P17" t="n">
-        <v>340.8873932595569</v>
+        <v>340.7936547877488</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -23899,28 +24002,28 @@
         <v>0.0385</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.7523283903024927</v>
+        <v>-0.7431987585267821</v>
       </c>
       <c r="J18" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K18" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1665591732623047</v>
+        <v>0.1641757194192989</v>
       </c>
       <c r="M18" t="n">
-        <v>9.636426671540759</v>
+        <v>9.638508726620344</v>
       </c>
       <c r="N18" t="n">
-        <v>168.7033854600098</v>
+        <v>168.3888646800345</v>
       </c>
       <c r="O18" t="n">
-        <v>12.98858673836418</v>
+        <v>12.97647350708329</v>
       </c>
       <c r="P18" t="n">
-        <v>341.5806426894617</v>
+        <v>341.4872396815892</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -23977,28 +24080,28 @@
         <v>0.0322</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.6948125738714708</v>
+        <v>-0.6750462249025857</v>
       </c>
       <c r="J19" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K19" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1184458843113624</v>
+        <v>0.1124718602652568</v>
       </c>
       <c r="M19" t="n">
-        <v>11.27669998562931</v>
+        <v>11.33923862119564</v>
       </c>
       <c r="N19" t="n">
-        <v>215.9300486031167</v>
+        <v>217.2409003648601</v>
       </c>
       <c r="O19" t="n">
-        <v>14.69455846914485</v>
+        <v>14.73909428577143</v>
       </c>
       <c r="P19" t="n">
-        <v>340.2288130421891</v>
+        <v>340.0280888927105</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -24055,28 +24158,28 @@
         <v>0.0311</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.6735082999555325</v>
+        <v>-0.6620448334342481</v>
       </c>
       <c r="J20" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K20" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1288143399690684</v>
+        <v>0.1256362252638759</v>
       </c>
       <c r="M20" t="n">
-        <v>10.89629774859381</v>
+        <v>10.9101666135471</v>
       </c>
       <c r="N20" t="n">
-        <v>186.6761470765977</v>
+        <v>186.5950573852596</v>
       </c>
       <c r="O20" t="n">
-        <v>13.66294796435226</v>
+        <v>13.65998013853825</v>
       </c>
       <c r="P20" t="n">
-        <v>344.7542027159246</v>
+        <v>344.6391855303079</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -24133,28 +24236,28 @@
         <v>0.0339</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5685104923424932</v>
+        <v>-0.5596573892233263</v>
       </c>
       <c r="J21" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K21" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1192437168321709</v>
+        <v>0.116672648364227</v>
       </c>
       <c r="M21" t="n">
-        <v>9.682101556349963</v>
+        <v>9.68974964780428</v>
       </c>
       <c r="N21" t="n">
-        <v>146.4773544441657</v>
+        <v>146.2684767582136</v>
       </c>
       <c r="O21" t="n">
-        <v>12.10278292146751</v>
+        <v>12.09415051825525</v>
       </c>
       <c r="P21" t="n">
-        <v>343.4825335437172</v>
+        <v>343.3942551151455</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -24211,28 +24314,28 @@
         <v>0.038</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.6685469041609772</v>
+        <v>-0.6597856975831122</v>
       </c>
       <c r="J22" t="n">
+        <v>214</v>
+      </c>
+      <c r="K22" t="n">
         <v>213</v>
       </c>
-      <c r="K22" t="n">
-        <v>212</v>
-      </c>
       <c r="L22" t="n">
-        <v>0.1545843510765177</v>
+        <v>0.1520487443115213</v>
       </c>
       <c r="M22" t="n">
-        <v>9.622474606349208</v>
+        <v>9.623302162277962</v>
       </c>
       <c r="N22" t="n">
-        <v>149.4927074783117</v>
+        <v>149.2604242710752</v>
       </c>
       <c r="O22" t="n">
-        <v>12.22672104361229</v>
+        <v>12.21721835243503</v>
       </c>
       <c r="P22" t="n">
-        <v>344.1341839100789</v>
+        <v>344.0467636609206</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -24289,28 +24392,28 @@
         <v>0.052</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.774982567614466</v>
+        <v>-0.7600268234251407</v>
       </c>
       <c r="J23" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K23" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1902270270166631</v>
+        <v>0.1844791271267746</v>
       </c>
       <c r="M23" t="n">
-        <v>9.992569861585615</v>
+        <v>10.02763087881366</v>
       </c>
       <c r="N23" t="n">
-        <v>157.0386380178251</v>
+        <v>157.674137927389</v>
       </c>
       <c r="O23" t="n">
-        <v>12.53150581605519</v>
+        <v>12.55683630248436</v>
       </c>
       <c r="P23" t="n">
-        <v>340.3886757280065</v>
+        <v>340.2397072303649</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -24367,28 +24470,28 @@
         <v>0.0404</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.4081926385112856</v>
+        <v>-0.3949813087284571</v>
       </c>
       <c r="J24" t="n">
+        <v>214</v>
+      </c>
+      <c r="K24" t="n">
         <v>213</v>
       </c>
-      <c r="K24" t="n">
-        <v>212</v>
-      </c>
       <c r="L24" t="n">
-        <v>0.06006215107241675</v>
+        <v>0.05662893829286275</v>
       </c>
       <c r="M24" t="n">
-        <v>10.05278167728122</v>
+        <v>10.07662482975439</v>
       </c>
       <c r="N24" t="n">
-        <v>159.4703988499969</v>
+        <v>159.7894300448473</v>
       </c>
       <c r="O24" t="n">
-        <v>12.62815896518558</v>
+        <v>12.64078439199274</v>
       </c>
       <c r="P24" t="n">
-        <v>340.6234867843506</v>
+        <v>340.4916627335122</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -24445,28 +24548,28 @@
         <v>0.0364</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1964492557151916</v>
+        <v>-0.1958896598267292</v>
       </c>
       <c r="J25" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K25" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L25" t="n">
-        <v>0.02842383128437465</v>
+        <v>0.02854248474412813</v>
       </c>
       <c r="M25" t="n">
-        <v>6.806658647500518</v>
+        <v>6.777001213476924</v>
       </c>
       <c r="N25" t="n">
-        <v>81.3554911272894</v>
+        <v>80.97184856506433</v>
       </c>
       <c r="O25" t="n">
-        <v>9.01972788543476</v>
+        <v>8.998435895480076</v>
       </c>
       <c r="P25" t="n">
-        <v>355.8087198393727</v>
+        <v>355.8031623531657</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -24523,28 +24626,28 @@
         <v>0.0501</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.428122685420282</v>
+        <v>-0.4168723155516156</v>
       </c>
       <c r="J26" t="n">
+        <v>214</v>
+      </c>
+      <c r="K26" t="n">
         <v>213</v>
       </c>
-      <c r="K26" t="n">
-        <v>212</v>
-      </c>
       <c r="L26" t="n">
-        <v>0.1146422491076797</v>
+        <v>0.1094490806791022</v>
       </c>
       <c r="M26" t="n">
-        <v>7.499688737523816</v>
+        <v>7.522495308905023</v>
       </c>
       <c r="N26" t="n">
-        <v>86.5689332414791</v>
+        <v>86.93678501574448</v>
       </c>
       <c r="O26" t="n">
-        <v>9.304242754866141</v>
+        <v>9.323989758453431</v>
       </c>
       <c r="P26" t="n">
-        <v>339.1943527905304</v>
+        <v>339.0820954058539</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -24601,28 +24704,28 @@
         <v>0.031</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.8601823765703365</v>
+        <v>-0.832652138775564</v>
       </c>
       <c r="J27" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K27" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L27" t="n">
-        <v>0.1243317488345285</v>
+        <v>0.1169746822061853</v>
       </c>
       <c r="M27" t="n">
-        <v>13.0158916875917</v>
+        <v>13.04809908272002</v>
       </c>
       <c r="N27" t="n">
-        <v>317.6781649955882</v>
+        <v>320.7553046080985</v>
       </c>
       <c r="O27" t="n">
-        <v>17.82352841037903</v>
+        <v>17.9096427828167</v>
       </c>
       <c r="P27" t="n">
-        <v>325.3922326068884</v>
+        <v>325.1167057125258</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -24679,28 +24782,28 @@
         <v>0.0477</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.4151821321844035</v>
+        <v>-0.3881761857374697</v>
       </c>
       <c r="J28" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K28" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L28" t="n">
-        <v>0.02755630890462568</v>
+        <v>0.02412658758984088</v>
       </c>
       <c r="M28" t="n">
-        <v>14.46779041653483</v>
+        <v>14.5197754603971</v>
       </c>
       <c r="N28" t="n">
-        <v>368.7903624532509</v>
+        <v>371.4623572691102</v>
       </c>
       <c r="O28" t="n">
-        <v>19.20391528968119</v>
+        <v>19.27335874384924</v>
       </c>
       <c r="P28" t="n">
-        <v>331.8674361601054</v>
+        <v>331.5958144493709</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -24738,7 +24841,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC214"/>
+  <dimension ref="A1:AC215"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56003,6 +56106,153 @@
         </is>
       </c>
     </row>
+    <row r="215">
+      <c r="A215" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:17:07+00:00</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>-35.26822824783478,173.1368570999463</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>-35.26750525372316,173.1365143478746</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>-35.26687718968372,173.13603334327127</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>-35.266242407498034,173.1355621164103</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>-35.265661339738934,173.13501266010124</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>-35.26506585479859,173.13448419368427</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>-35.26449583565258,173.13391863608203</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>-35.26389397602194,173.1333994416959</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>-35.26339381598237,173.1327321377239</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>-35.26285128017729,173.13212653929935</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>-35.26214058714173,173.13176582087928</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>-35.26162409169284,173.13112228906743</t>
+        </is>
+      </c>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>-35.261008205801005,173.13062349263865</t>
+        </is>
+      </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>-35.26044203826589,173.13005228630945</t>
+        </is>
+      </c>
+      <c r="P215" t="inlineStr">
+        <is>
+          <t>-35.259890106105395,173.12946034348556</t>
+        </is>
+      </c>
+      <c r="Q215" t="inlineStr">
+        <is>
+          <t>-35.259295510277866,173.12893052560287</t>
+        </is>
+      </c>
+      <c r="R215" t="inlineStr">
+        <is>
+          <t>-35.25868973945817,173.128416976033</t>
+        </is>
+      </c>
+      <c r="S215" t="inlineStr">
+        <is>
+          <t>-35.25819839859074,173.12773677772597</t>
+        </is>
+      </c>
+      <c r="T215" t="inlineStr">
+        <is>
+          <t>-35.25761206863737,173.12719490536207</t>
+        </is>
+      </c>
+      <c r="U215" t="inlineStr">
+        <is>
+          <t>-35.25704153673214,173.12663002076198</t>
+        </is>
+      </c>
+      <c r="V215" t="inlineStr">
+        <is>
+          <t>-35.256466659872025,173.12607145801476</t>
+        </is>
+      </c>
+      <c r="W215" t="inlineStr">
+        <is>
+          <t>-35.25590729142208,173.125490304808</t>
+        </is>
+      </c>
+      <c r="X215" t="inlineStr">
+        <is>
+          <t>-35.25539132985073,173.12484593264074</t>
+        </is>
+      </c>
+      <c r="Y215" t="inlineStr">
+        <is>
+          <t>-35.25486529267431,173.12421622767508</t>
+        </is>
+      </c>
+      <c r="Z215" t="inlineStr">
+        <is>
+          <t>-35.254241896211894,173.12372830129252</t>
+        </is>
+      </c>
+      <c r="AA215" t="inlineStr">
+        <is>
+          <t>-35.25363904384924,173.12321045083348</t>
+        </is>
+      </c>
+      <c r="AB215" t="inlineStr">
+        <is>
+          <t>-35.253179904120756,173.1224833060374</t>
+        </is>
+      </c>
+      <c r="AC215" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0065/nzd0065.xlsx
+++ b/data/nzd0065/nzd0065.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC215"/>
+  <dimension ref="A1:AC216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20299,10 +20299,10 @@
         <v>424.85</v>
       </c>
       <c r="C215" t="n">
-        <v>397.11</v>
+        <v>386.15</v>
       </c>
       <c r="D215" t="n">
-        <v>385.77</v>
+        <v>376.48</v>
       </c>
       <c r="E215" t="n">
         <v>373.27</v>
@@ -20320,10 +20320,10 @@
         <v>356.22</v>
       </c>
       <c r="J215" t="n">
-        <v>366.98</v>
+        <v>356.69</v>
       </c>
       <c r="K215" t="n">
-        <v>370.42</v>
+        <v>356.08</v>
       </c>
       <c r="L215" t="n">
         <v>344.81</v>
@@ -20347,7 +20347,7 @@
         <v>331.67</v>
       </c>
       <c r="S215" t="n">
-        <v>343.96</v>
+        <v>331.56</v>
       </c>
       <c r="T215" t="n">
         <v>339.84</v>
@@ -20359,10 +20359,10 @@
         <v>336.31</v>
       </c>
       <c r="W215" t="n">
-        <v>336.85</v>
+        <v>326.2</v>
       </c>
       <c r="X215" t="n">
-        <v>344.89</v>
+        <v>333.42</v>
       </c>
       <c r="Y215" t="n">
         <v>351.19</v>
@@ -20379,6 +20379,99 @@
       <c r="AC215" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B216" t="n">
+        <v>415.04</v>
+      </c>
+      <c r="C216" t="n">
+        <v>385.5</v>
+      </c>
+      <c r="D216" t="n">
+        <v>374.77</v>
+      </c>
+      <c r="E216" t="n">
+        <v>371.19</v>
+      </c>
+      <c r="F216" t="n">
+        <v>368.64</v>
+      </c>
+      <c r="G216" t="n">
+        <v>363.67</v>
+      </c>
+      <c r="H216" t="n">
+        <v>362.02</v>
+      </c>
+      <c r="I216" t="n">
+        <v>356.8</v>
+      </c>
+      <c r="J216" t="n">
+        <v>355.24</v>
+      </c>
+      <c r="K216" t="n">
+        <v>351.33</v>
+      </c>
+      <c r="L216" t="n">
+        <v>343.17</v>
+      </c>
+      <c r="M216" t="n">
+        <v>350.6</v>
+      </c>
+      <c r="N216" t="n">
+        <v>341.49</v>
+      </c>
+      <c r="O216" t="n">
+        <v>340.35</v>
+      </c>
+      <c r="P216" t="n">
+        <v>341.58</v>
+      </c>
+      <c r="Q216" t="n">
+        <v>338.45</v>
+      </c>
+      <c r="R216" t="n">
+        <v>329.47</v>
+      </c>
+      <c r="S216" t="n">
+        <v>330.13</v>
+      </c>
+      <c r="T216" t="n">
+        <v>339.17</v>
+      </c>
+      <c r="U216" t="n">
+        <v>338.87</v>
+      </c>
+      <c r="V216" t="n">
+        <v>337.4</v>
+      </c>
+      <c r="W216" t="n">
+        <v>322.55</v>
+      </c>
+      <c r="X216" t="n">
+        <v>332.2</v>
+      </c>
+      <c r="Y216" t="n">
+        <v>353.26</v>
+      </c>
+      <c r="Z216" t="n">
+        <v>339.88</v>
+      </c>
+      <c r="AA216" t="n">
+        <v>333.7</v>
+      </c>
+      <c r="AB216" t="n">
+        <v>348.32</v>
+      </c>
+      <c r="AC216" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -20393,7 +20486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B219"/>
+  <dimension ref="A1:B220"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22586,6 +22679,16 @@
       </c>
       <c r="B219" t="n">
         <v>-0.71</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B220" t="n">
+        <v>-0.51</v>
       </c>
     </row>
   </sheetData>
@@ -22754,28 +22857,28 @@
         <v>0.0257</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.8268173668510771</v>
+        <v>-0.7982775385578228</v>
       </c>
       <c r="J2" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K2" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L2" t="n">
-        <v>0.07926167596613221</v>
+        <v>0.07426580369276581</v>
       </c>
       <c r="M2" t="n">
-        <v>15.88362196899181</v>
+        <v>15.95568749508896</v>
       </c>
       <c r="N2" t="n">
-        <v>489.1600434547032</v>
+        <v>491.861427951183</v>
       </c>
       <c r="O2" t="n">
-        <v>22.1169627990532</v>
+        <v>22.17794913762729</v>
       </c>
       <c r="P2" t="n">
-        <v>404.4775135694399</v>
+        <v>404.190488867111</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -22832,28 +22935,28 @@
         <v>0.0356</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4914582342201636</v>
+        <v>-0.4874527917179469</v>
       </c>
       <c r="J3" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K3" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06081625501557697</v>
+        <v>0.06072619375454835</v>
       </c>
       <c r="M3" t="n">
-        <v>11.56009346625804</v>
+        <v>11.52266724326401</v>
       </c>
       <c r="N3" t="n">
-        <v>231.0990526356215</v>
+        <v>228.9086631369928</v>
       </c>
       <c r="O3" t="n">
-        <v>15.20194239679988</v>
+        <v>15.12972779454385</v>
       </c>
       <c r="P3" t="n">
-        <v>383.2223243004132</v>
+        <v>383.1817964374433</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -22910,28 +23013,28 @@
         <v>0.0412</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1746914447520918</v>
+        <v>-0.1779528291112625</v>
       </c>
       <c r="J4" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K4" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0121842151317072</v>
+        <v>0.01283732381078684</v>
       </c>
       <c r="M4" t="n">
-        <v>9.753631235584772</v>
+        <v>9.692230213716675</v>
       </c>
       <c r="N4" t="n">
-        <v>152.7920883707046</v>
+        <v>151.1851480701004</v>
       </c>
       <c r="O4" t="n">
-        <v>12.36090969025761</v>
+        <v>12.29573698767587</v>
       </c>
       <c r="P4" t="n">
-        <v>374.0244698183045</v>
+        <v>374.0566698052141</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -22988,28 +23091,28 @@
         <v>0.0423</v>
       </c>
       <c r="I5" t="n">
-        <v>0.002564785287642266</v>
+        <v>0.006113477404071254</v>
       </c>
       <c r="J5" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K5" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L5" t="n">
-        <v>2.839216602934513e-06</v>
+        <v>1.628471369885531e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>9.746302517506674</v>
+        <v>9.716197097700801</v>
       </c>
       <c r="N5" t="n">
-        <v>143.0808327227401</v>
+        <v>142.4867654934017</v>
       </c>
       <c r="O5" t="n">
-        <v>11.96164005154561</v>
+        <v>11.93678204096069</v>
       </c>
       <c r="P5" t="n">
-        <v>367.027527427361</v>
+        <v>366.9920367785357</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -23066,28 +23169,28 @@
         <v>0.0459</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.03467572894923878</v>
+        <v>-0.03154835502869521</v>
       </c>
       <c r="J6" t="n">
+        <v>215</v>
+      </c>
+      <c r="K6" t="n">
         <v>214</v>
       </c>
-      <c r="K6" t="n">
-        <v>213</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.0005277819815435736</v>
+        <v>0.0004410848652368626</v>
       </c>
       <c r="M6" t="n">
-        <v>9.576315476068089</v>
+        <v>9.544964828841369</v>
       </c>
       <c r="N6" t="n">
-        <v>140.3522997897001</v>
+        <v>139.7571228419286</v>
       </c>
       <c r="O6" t="n">
-        <v>11.84703759552151</v>
+        <v>11.82189167781234</v>
       </c>
       <c r="P6" t="n">
-        <v>365.9400677140811</v>
+        <v>365.9087111891496</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -23144,28 +23247,28 @@
         <v>0.0435</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.07705316900180027</v>
+        <v>-0.07517322947316427</v>
       </c>
       <c r="J7" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K7" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L7" t="n">
-        <v>0.003451281904765069</v>
+        <v>0.00331743421819497</v>
       </c>
       <c r="M7" t="n">
-        <v>7.871015814062355</v>
+        <v>7.843656803591482</v>
       </c>
       <c r="N7" t="n">
-        <v>105.2031354435851</v>
+        <v>104.7356845744683</v>
       </c>
       <c r="O7" t="n">
-        <v>10.25685797130803</v>
+        <v>10.23404536703196</v>
       </c>
       <c r="P7" t="n">
-        <v>363.5606914908464</v>
+        <v>363.5417891042437</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -23222,28 +23325,28 @@
         <v>0.041</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01983018385054353</v>
+        <v>0.02141659642383405</v>
       </c>
       <c r="J8" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K8" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0003094279451482107</v>
+        <v>0.0003644221468016573</v>
       </c>
       <c r="M8" t="n">
-        <v>7.054590494117666</v>
+        <v>7.031536174508512</v>
       </c>
       <c r="N8" t="n">
-        <v>77.96310332850479</v>
+        <v>77.61605517725502</v>
       </c>
       <c r="O8" t="n">
-        <v>8.829671756554985</v>
+        <v>8.809997456143504</v>
       </c>
       <c r="P8" t="n">
-        <v>359.6479925732286</v>
+        <v>359.6320415368708</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -23300,28 +23403,28 @@
         <v>0.0357</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2661141596553411</v>
+        <v>-0.2611058468289939</v>
       </c>
       <c r="J9" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K9" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03572763599091744</v>
+        <v>0.03472827958573055</v>
       </c>
       <c r="M9" t="n">
-        <v>9.045723851182744</v>
+        <v>9.029430697353686</v>
       </c>
       <c r="N9" t="n">
-        <v>117.2899982061304</v>
+        <v>116.899653880914</v>
       </c>
       <c r="O9" t="n">
-        <v>10.83005070191873</v>
+        <v>10.81201433040643</v>
       </c>
       <c r="P9" t="n">
-        <v>358.1371480955691</v>
+        <v>358.0867905900064</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -23378,28 +23481,28 @@
         <v>0.0255</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1685233997598322</v>
+        <v>-0.1660747472795427</v>
       </c>
       <c r="J10" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K10" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L10" t="n">
-        <v>0.008837593727678783</v>
+        <v>0.008718044720948059</v>
       </c>
       <c r="M10" t="n">
-        <v>10.96458881368194</v>
+        <v>10.92615676563149</v>
       </c>
       <c r="N10" t="n">
-        <v>195.4613013509803</v>
+        <v>193.4634937659018</v>
       </c>
       <c r="O10" t="n">
-        <v>13.98074752475633</v>
+        <v>13.90911549186007</v>
       </c>
       <c r="P10" t="n">
-        <v>346.7246625158868</v>
+        <v>346.6995823561588</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -23456,28 +23559,28 @@
         <v>0.0232</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2888338325029592</v>
+        <v>-0.2872411898121419</v>
       </c>
       <c r="J11" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K11" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L11" t="n">
-        <v>0.02031890963791227</v>
+        <v>0.02050297654681954</v>
       </c>
       <c r="M11" t="n">
-        <v>12.54770671353088</v>
+        <v>12.49768009230198</v>
       </c>
       <c r="N11" t="n">
-        <v>246.8368671807528</v>
+        <v>243.1606846457792</v>
       </c>
       <c r="O11" t="n">
-        <v>15.71104284192341</v>
+        <v>15.59361037879872</v>
       </c>
       <c r="P11" t="n">
-        <v>343.0408826180629</v>
+        <v>343.0242292714098</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -23534,28 +23637,28 @@
         <v>0.031</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.3448552428914346</v>
+        <v>-0.3390271759176495</v>
       </c>
       <c r="J12" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K12" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L12" t="n">
-        <v>0.04584241744987982</v>
+        <v>0.04473743923290263</v>
       </c>
       <c r="M12" t="n">
-        <v>10.0907507449108</v>
+        <v>10.07932624273981</v>
       </c>
       <c r="N12" t="n">
-        <v>151.8993214558444</v>
+        <v>151.4029639762769</v>
       </c>
       <c r="O12" t="n">
-        <v>12.32474427547462</v>
+        <v>12.30459117469072</v>
       </c>
       <c r="P12" t="n">
-        <v>345.6669133271917</v>
+        <v>345.6083133704341</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -23612,28 +23715,28 @@
         <v>0.036</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2671672683870558</v>
+        <v>-0.2556330724822458</v>
       </c>
       <c r="J13" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K13" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L13" t="n">
-        <v>0.02672018112986041</v>
+        <v>0.02463209684879486</v>
       </c>
       <c r="M13" t="n">
-        <v>9.972240126281546</v>
+        <v>9.99451236496061</v>
       </c>
       <c r="N13" t="n">
-        <v>159.5491130258649</v>
+        <v>159.6301325101529</v>
       </c>
       <c r="O13" t="n">
-        <v>12.6312751939725</v>
+        <v>12.63448188530709</v>
       </c>
       <c r="P13" t="n">
-        <v>344.3757523922698</v>
+        <v>344.259778539482</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -23690,28 +23793,28 @@
         <v>0.0414</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2986938417975329</v>
+        <v>-0.2895137174823704</v>
       </c>
       <c r="J14" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K14" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L14" t="n">
-        <v>0.03044892369422725</v>
+        <v>0.0288521483992169</v>
       </c>
       <c r="M14" t="n">
-        <v>10.64320895688575</v>
+        <v>10.63914992244555</v>
       </c>
       <c r="N14" t="n">
-        <v>174.3335034973459</v>
+        <v>174.0440601678796</v>
       </c>
       <c r="O14" t="n">
-        <v>13.2035413241049</v>
+        <v>13.19257594891459</v>
       </c>
       <c r="P14" t="n">
-        <v>338.8479549172054</v>
+        <v>338.7556507466601</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -23768,28 +23871,28 @@
         <v>0.042</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3212595948569906</v>
+        <v>-0.3102305093679493</v>
       </c>
       <c r="J15" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K15" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L15" t="n">
-        <v>0.02974367212700291</v>
+        <v>0.02795989690715828</v>
       </c>
       <c r="M15" t="n">
-        <v>11.70949581744113</v>
+        <v>11.69901082809663</v>
       </c>
       <c r="N15" t="n">
-        <v>207.217355825719</v>
+        <v>206.9992977535439</v>
       </c>
       <c r="O15" t="n">
-        <v>14.39504622520258</v>
+        <v>14.38747016516607</v>
       </c>
       <c r="P15" t="n">
-        <v>336.2007295207246</v>
+        <v>336.0894381287795</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -23846,28 +23949,28 @@
         <v>0.0418</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3133482410937986</v>
+        <v>-0.2978610948017917</v>
       </c>
       <c r="J16" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K16" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L16" t="n">
-        <v>0.02494298885408908</v>
+        <v>0.02266961329513451</v>
       </c>
       <c r="M16" t="n">
-        <v>12.6620397508207</v>
+        <v>12.66728988786448</v>
       </c>
       <c r="N16" t="n">
-        <v>237.107371243429</v>
+        <v>237.4895398808372</v>
       </c>
       <c r="O16" t="n">
-        <v>15.3982911793299</v>
+        <v>15.4106956326065</v>
       </c>
       <c r="P16" t="n">
-        <v>332.0452278372112</v>
+        <v>331.8891135434303</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -23924,28 +24027,28 @@
         <v>0.0382</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.453623192183824</v>
+        <v>-0.4450432221377131</v>
       </c>
       <c r="J17" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K17" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L17" t="n">
-        <v>0.09504334948697379</v>
+        <v>0.09232534921920132</v>
       </c>
       <c r="M17" t="n">
-        <v>8.524579115198328</v>
+        <v>8.521851580856694</v>
       </c>
       <c r="N17" t="n">
-        <v>120.1320816386303</v>
+        <v>120.0159666545293</v>
       </c>
       <c r="O17" t="n">
-        <v>10.96047816651401</v>
+        <v>10.95517990060087</v>
       </c>
       <c r="P17" t="n">
-        <v>340.7936547877488</v>
+        <v>340.7069406578555</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -24002,28 +24105,28 @@
         <v>0.0385</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.7431987585267821</v>
+        <v>-0.7361316309003275</v>
       </c>
       <c r="J18" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K18" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1641757194192989</v>
+        <v>0.1626990403415314</v>
       </c>
       <c r="M18" t="n">
-        <v>9.638508726620344</v>
+        <v>9.629942815667373</v>
       </c>
       <c r="N18" t="n">
-        <v>168.3888646800345</v>
+        <v>167.8838416054521</v>
       </c>
       <c r="O18" t="n">
-        <v>12.97647350708329</v>
+        <v>12.95699971465046</v>
       </c>
       <c r="P18" t="n">
-        <v>341.4872396815892</v>
+        <v>341.4145702378786</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -24080,28 +24183,28 @@
         <v>0.0322</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.6750462249025857</v>
+        <v>-0.6786007088873214</v>
       </c>
       <c r="J19" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K19" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1124718602652568</v>
+        <v>0.1152639139634135</v>
       </c>
       <c r="M19" t="n">
-        <v>11.33923862119564</v>
+        <v>11.26429296619805</v>
       </c>
       <c r="N19" t="n">
-        <v>217.2409003648601</v>
+        <v>214.6752860481217</v>
       </c>
       <c r="O19" t="n">
-        <v>14.73909428577143</v>
+        <v>14.65180146084848</v>
       </c>
       <c r="P19" t="n">
-        <v>340.0280888927105</v>
+        <v>340.063798663333</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -24158,28 +24261,28 @@
         <v>0.0311</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.6620448334342481</v>
+        <v>-0.651326452429705</v>
       </c>
       <c r="J20" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K20" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1256362252638759</v>
+        <v>0.1227626659866919</v>
       </c>
       <c r="M20" t="n">
-        <v>10.9101666135471</v>
+        <v>10.92049882619608</v>
       </c>
       <c r="N20" t="n">
-        <v>186.5950573852596</v>
+        <v>186.4217945157786</v>
       </c>
       <c r="O20" t="n">
-        <v>13.65998013853825</v>
+        <v>13.65363667730245</v>
       </c>
       <c r="P20" t="n">
-        <v>344.6391855303079</v>
+        <v>344.5310905827832</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -24236,28 +24339,28 @@
         <v>0.0339</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5596573892233263</v>
+        <v>-0.550559863603156</v>
       </c>
       <c r="J21" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K21" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L21" t="n">
-        <v>0.116672648364227</v>
+        <v>0.1139882193877415</v>
       </c>
       <c r="M21" t="n">
-        <v>9.68974964780428</v>
+        <v>9.698317843271216</v>
       </c>
       <c r="N21" t="n">
-        <v>146.2684767582136</v>
+        <v>146.093620342484</v>
       </c>
       <c r="O21" t="n">
-        <v>12.09415051825525</v>
+        <v>12.08691939008795</v>
       </c>
       <c r="P21" t="n">
-        <v>343.3942551151455</v>
+        <v>343.3030684248171</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -24314,28 +24417,28 @@
         <v>0.038</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.6597856975831122</v>
+        <v>-0.6501934232901585</v>
       </c>
       <c r="J22" t="n">
+        <v>215</v>
+      </c>
+      <c r="K22" t="n">
         <v>214</v>
       </c>
-      <c r="K22" t="n">
-        <v>213</v>
-      </c>
       <c r="L22" t="n">
-        <v>0.1520487443115213</v>
+        <v>0.1490949506094421</v>
       </c>
       <c r="M22" t="n">
-        <v>9.623302162277962</v>
+        <v>9.628027456881867</v>
       </c>
       <c r="N22" t="n">
-        <v>149.2604242710752</v>
+        <v>149.1289543116255</v>
       </c>
       <c r="O22" t="n">
-        <v>12.21721835243503</v>
+        <v>12.2118366477621</v>
       </c>
       <c r="P22" t="n">
-        <v>344.0467636609206</v>
+        <v>343.9505576934719</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -24392,28 +24495,28 @@
         <v>0.052</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.7600268234251407</v>
+        <v>-0.7667889229943277</v>
       </c>
       <c r="J23" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K23" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1844791271267746</v>
+        <v>0.1897940089853503</v>
       </c>
       <c r="M23" t="n">
-        <v>10.02763087881366</v>
+        <v>9.943441796729804</v>
       </c>
       <c r="N23" t="n">
-        <v>157.674137927389</v>
+        <v>155.8013131270703</v>
       </c>
       <c r="O23" t="n">
-        <v>12.55683630248436</v>
+        <v>12.4820396220758</v>
       </c>
       <c r="P23" t="n">
-        <v>340.2397072303649</v>
+        <v>340.3069326174346</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -24470,28 +24573,28 @@
         <v>0.0404</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.3949813087284571</v>
+        <v>-0.4028038650970511</v>
       </c>
       <c r="J24" t="n">
+        <v>215</v>
+      </c>
+      <c r="K24" t="n">
         <v>214</v>
       </c>
-      <c r="K24" t="n">
-        <v>213</v>
-      </c>
       <c r="L24" t="n">
-        <v>0.05662893829286275</v>
+        <v>0.0596589526251573</v>
       </c>
       <c r="M24" t="n">
-        <v>10.07662482975439</v>
+        <v>9.987541366452673</v>
       </c>
       <c r="N24" t="n">
-        <v>159.7894300448473</v>
+        <v>158.0722701936876</v>
       </c>
       <c r="O24" t="n">
-        <v>12.64078439199274</v>
+        <v>12.57267951526991</v>
       </c>
       <c r="P24" t="n">
-        <v>340.4916627335122</v>
+        <v>340.5696062576222</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -24548,28 +24651,28 @@
         <v>0.0364</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1958896598267292</v>
+        <v>-0.1935278301883103</v>
       </c>
       <c r="J25" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K25" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L25" t="n">
-        <v>0.02854248474412813</v>
+        <v>0.02813836371283596</v>
       </c>
       <c r="M25" t="n">
-        <v>6.777001213476924</v>
+        <v>6.755854247568617</v>
       </c>
       <c r="N25" t="n">
-        <v>80.97184856506433</v>
+        <v>80.6244533559107</v>
       </c>
       <c r="O25" t="n">
-        <v>8.998435895480076</v>
+        <v>8.979112058322398</v>
       </c>
       <c r="P25" t="n">
-        <v>355.8031623531657</v>
+        <v>355.7795840342011</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -24626,28 +24729,28 @@
         <v>0.0501</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4168723155516156</v>
+        <v>-0.4064906064320072</v>
       </c>
       <c r="J26" t="n">
+        <v>215</v>
+      </c>
+      <c r="K26" t="n">
         <v>214</v>
       </c>
-      <c r="K26" t="n">
-        <v>213</v>
-      </c>
       <c r="L26" t="n">
-        <v>0.1094490806791022</v>
+        <v>0.1048505919015186</v>
       </c>
       <c r="M26" t="n">
-        <v>7.522495308905023</v>
+        <v>7.540071346562805</v>
       </c>
       <c r="N26" t="n">
-        <v>86.93678501574448</v>
+        <v>87.19354458749375</v>
       </c>
       <c r="O26" t="n">
-        <v>9.323989758453431</v>
+        <v>9.337748368182437</v>
       </c>
       <c r="P26" t="n">
-        <v>339.0820954058539</v>
+        <v>338.9779717810367</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -24704,28 +24807,28 @@
         <v>0.031</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.832652138775564</v>
+        <v>-0.8055887730997489</v>
       </c>
       <c r="J27" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K27" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L27" t="n">
-        <v>0.1169746822061853</v>
+        <v>0.1099495986324776</v>
       </c>
       <c r="M27" t="n">
-        <v>13.04809908272002</v>
+        <v>13.07726129688534</v>
       </c>
       <c r="N27" t="n">
-        <v>320.7553046080985</v>
+        <v>323.696387815509</v>
       </c>
       <c r="O27" t="n">
-        <v>17.9096427828167</v>
+        <v>17.99156435153733</v>
       </c>
       <c r="P27" t="n">
-        <v>325.1167057125258</v>
+        <v>324.8444582374207</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -24782,28 +24885,28 @@
         <v>0.0477</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.3881761857374697</v>
+        <v>-0.3644927769154966</v>
       </c>
       <c r="J28" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K28" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L28" t="n">
-        <v>0.02412658758984088</v>
+        <v>0.02135076655527202</v>
       </c>
       <c r="M28" t="n">
-        <v>14.5197754603971</v>
+        <v>14.55639408833556</v>
       </c>
       <c r="N28" t="n">
-        <v>371.4623572691102</v>
+        <v>373.1300600553971</v>
       </c>
       <c r="O28" t="n">
-        <v>19.27335874384924</v>
+        <v>19.3165747495615</v>
       </c>
       <c r="P28" t="n">
-        <v>331.5958144493709</v>
+        <v>331.3563898632346</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -24841,7 +24944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC215"/>
+  <dimension ref="A1:AC216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56119,12 +56222,12 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>-35.26750525372316,173.1365143478746</t>
+          <t>-35.267441810497346,173.13660673977893</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>-35.26687718968372,173.13603334327127</t>
+          <t>-35.266823413625914,173.13611165680373</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -56154,12 +56257,12 @@
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>-35.26339381598237,173.1327321377239</t>
+          <t>-35.26333425279116,173.13281887895678</t>
         </is>
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t>-35.26285128017729,173.13212653929935</t>
+          <t>-35.26276827412647,173.13224742024235</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
@@ -56199,7 +56302,7 @@
       </c>
       <c r="S215" t="inlineStr">
         <is>
-          <t>-35.25819839859074,173.12773677772597</t>
+          <t>-35.2581266244409,173.12784130169027</t>
         </is>
       </c>
       <c r="T215" t="inlineStr">
@@ -56219,12 +56322,12 @@
       </c>
       <c r="W215" t="inlineStr">
         <is>
-          <t>-35.25590729142208,173.125490304808</t>
+          <t>-35.25584564773922,173.12558007599074</t>
         </is>
       </c>
       <c r="X215" t="inlineStr">
         <is>
-          <t>-35.25539132985073,173.12484593264074</t>
+          <t>-35.25532494023878,173.12494261552825</t>
         </is>
       </c>
       <c r="Y215" t="inlineStr">
@@ -56250,6 +56353,153 @@
       <c r="AC215" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>-35.26817146142966,173.13693979808545</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>-35.26743804789505,173.1366122192213</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>-35.266813515121044,173.13612607187756</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>-35.26623036726045,173.1355796504615</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>-35.265653177880786,173.1350245461157</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>-35.26506197648387,173.13448984162326</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>-35.26448998926281,173.13392715010588</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>-35.26389733334191,173.13339455247683</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>-35.26332585952791,173.132831101958</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>-35.262740779068935,173.1322874609466</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>-35.26213109414391,173.13177964538875</t>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>-35.26161164666897,173.13114041261457</t>
+        </is>
+      </c>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>-35.26099645542407,173.13064060455298</t>
+        </is>
+      </c>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>-35.26042739377089,173.13007361289897</t>
+        </is>
+      </c>
+      <c r="P216" t="inlineStr">
+        <is>
+          <t>-35.25987204657361,173.12948664337733</t>
+        </is>
+      </c>
+      <c r="Q216" t="inlineStr">
+        <is>
+          <t>-35.25929145847596,173.128936426194</t>
+        </is>
+      </c>
+      <c r="R216" t="inlineStr">
+        <is>
+          <t>-35.258677005269206,173.12843552065735</t>
+        </is>
+      </c>
+      <c r="S216" t="inlineStr">
+        <is>
+          <t>-35.25811834725489,173.12785335565172</t>
+        </is>
+      </c>
+      <c r="T216" t="inlineStr">
+        <is>
+          <t>-35.25760819053583,173.1272005530083</t>
+        </is>
+      </c>
+      <c r="U216" t="inlineStr">
+        <is>
+          <t>-35.25704396777032,173.12662648046006</t>
+        </is>
+      </c>
+      <c r="V216" t="inlineStr">
+        <is>
+          <t>-35.256472968968254,173.1260622701249</t>
+        </is>
+      </c>
+      <c r="W216" t="inlineStr">
+        <is>
+          <t>-35.25582452101561,173.1256108426089</t>
+        </is>
+      </c>
+      <c r="X216" t="inlineStr">
+        <is>
+          <t>-35.255317878741046,173.1249528991391</t>
+        </is>
+      </c>
+      <c r="Y216" t="inlineStr">
+        <is>
+          <t>-35.25487727399132,173.12419877927013</t>
+        </is>
+      </c>
+      <c r="Z216" t="inlineStr">
+        <is>
+          <t>-35.25423732364661,173.12373496030952</t>
+        </is>
+      </c>
+      <c r="AA216" t="inlineStr">
+        <is>
+          <t>-35.25363904384924,173.12321045083348</t>
+        </is>
+      </c>
+      <c r="AB216" t="inlineStr">
+        <is>
+          <t>-35.25316115099927,173.1225106162705</t>
+        </is>
+      </c>
+      <c r="AC216" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>

--- a/data/nzd0065/nzd0065.xlsx
+++ b/data/nzd0065/nzd0065.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC216"/>
+  <dimension ref="A1:AC217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20475,6 +20475,99 @@
         </is>
       </c>
     </row>
+    <row r="217">
+      <c r="A217" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:17:49+00:00</t>
+        </is>
+      </c>
+      <c r="B217" t="n">
+        <v>404.25</v>
+      </c>
+      <c r="C217" t="n">
+        <v>382.81</v>
+      </c>
+      <c r="D217" t="n">
+        <v>373.06</v>
+      </c>
+      <c r="E217" t="n">
+        <v>370.54</v>
+      </c>
+      <c r="F217" t="n">
+        <v>366.52</v>
+      </c>
+      <c r="G217" t="n">
+        <v>361.41</v>
+      </c>
+      <c r="H217" t="n">
+        <v>359.41</v>
+      </c>
+      <c r="I217" t="n">
+        <v>353.17</v>
+      </c>
+      <c r="J217" t="n">
+        <v>350.44</v>
+      </c>
+      <c r="K217" t="n">
+        <v>345.41</v>
+      </c>
+      <c r="L217" t="n">
+        <v>339.36</v>
+      </c>
+      <c r="M217" t="n">
+        <v>347.55</v>
+      </c>
+      <c r="N217" t="n">
+        <v>338.99</v>
+      </c>
+      <c r="O217" t="n">
+        <v>337.48</v>
+      </c>
+      <c r="P217" t="n">
+        <v>339.66</v>
+      </c>
+      <c r="Q217" t="n">
+        <v>334.06</v>
+      </c>
+      <c r="R217" t="n">
+        <v>326.32</v>
+      </c>
+      <c r="S217" t="n">
+        <v>330.13</v>
+      </c>
+      <c r="T217" t="n">
+        <v>336.72</v>
+      </c>
+      <c r="U217" t="n">
+        <v>336.53</v>
+      </c>
+      <c r="V217" t="n">
+        <v>336.1</v>
+      </c>
+      <c r="W217" t="n">
+        <v>318.26</v>
+      </c>
+      <c r="X217" t="n">
+        <v>327.76</v>
+      </c>
+      <c r="Y217" t="n">
+        <v>353.26</v>
+      </c>
+      <c r="Z217" t="n">
+        <v>337.9</v>
+      </c>
+      <c r="AA217" t="n">
+        <v>330.41</v>
+      </c>
+      <c r="AB217" t="n">
+        <v>343.84</v>
+      </c>
+      <c r="AC217" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -20486,7 +20579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B220"/>
+  <dimension ref="A1:B221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22689,6 +22782,16 @@
       </c>
       <c r="B220" t="n">
         <v>-0.51</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B221" t="n">
+        <v>-0.78</v>
       </c>
     </row>
   </sheetData>
@@ -22857,28 +22960,28 @@
         <v>0.0257</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.7982775385578228</v>
+        <v>-0.7797225421251618</v>
       </c>
       <c r="J2" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K2" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L2" t="n">
-        <v>0.07426580369276581</v>
+        <v>0.07145900984401288</v>
       </c>
       <c r="M2" t="n">
-        <v>15.95568749508896</v>
+        <v>15.97718873349755</v>
       </c>
       <c r="N2" t="n">
-        <v>491.861427951183</v>
+        <v>491.699330520014</v>
       </c>
       <c r="O2" t="n">
-        <v>22.17794913762729</v>
+        <v>22.17429436351953</v>
       </c>
       <c r="P2" t="n">
-        <v>404.190488867111</v>
+        <v>404.0034939000066</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -22935,28 +23038,28 @@
         <v>0.0356</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4874527917179469</v>
+        <v>-0.4765369440133842</v>
       </c>
       <c r="J3" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K3" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06072619375454835</v>
+        <v>0.0585553028926189</v>
       </c>
       <c r="M3" t="n">
-        <v>11.52266724326401</v>
+        <v>11.5159404599341</v>
       </c>
       <c r="N3" t="n">
-        <v>228.9086631369928</v>
+        <v>228.5855072593669</v>
       </c>
       <c r="O3" t="n">
-        <v>15.12972779454385</v>
+        <v>15.11904452203799</v>
       </c>
       <c r="P3" t="n">
-        <v>383.1817964374433</v>
+        <v>383.0724703897253</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -23013,28 +23116,28 @@
         <v>0.0412</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1779528291112625</v>
+        <v>-0.1747054361915979</v>
       </c>
       <c r="J4" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K4" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01283732381078684</v>
+        <v>0.01249499922565356</v>
       </c>
       <c r="M4" t="n">
-        <v>9.692230213716675</v>
+        <v>9.661940112582782</v>
       </c>
       <c r="N4" t="n">
-        <v>151.1851480701004</v>
+        <v>150.5448336487452</v>
       </c>
       <c r="O4" t="n">
-        <v>12.29573698767587</v>
+        <v>12.26967129342694</v>
       </c>
       <c r="P4" t="n">
-        <v>374.0566698052141</v>
+        <v>374.0241253879389</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -23091,28 +23194,28 @@
         <v>0.0423</v>
       </c>
       <c r="I5" t="n">
-        <v>0.006113477404071254</v>
+        <v>0.009009449206305019</v>
       </c>
       <c r="J5" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K5" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L5" t="n">
-        <v>1.628471369885531e-05</v>
+        <v>3.570503611938225e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>9.716197097700801</v>
+        <v>9.683447222966658</v>
       </c>
       <c r="N5" t="n">
-        <v>142.4867654934017</v>
+        <v>141.8735536750279</v>
       </c>
       <c r="O5" t="n">
-        <v>11.93678204096069</v>
+        <v>11.9110685362409</v>
       </c>
       <c r="P5" t="n">
-        <v>366.9920367785357</v>
+        <v>366.9630142003996</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -23169,28 +23272,28 @@
         <v>0.0459</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.03154835502869521</v>
+        <v>-0.0303005037928844</v>
       </c>
       <c r="J6" t="n">
+        <v>216</v>
+      </c>
+      <c r="K6" t="n">
         <v>215</v>
       </c>
-      <c r="K6" t="n">
-        <v>214</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.0004410848652368626</v>
+        <v>0.0004108823440162057</v>
       </c>
       <c r="M6" t="n">
-        <v>9.544964828841369</v>
+        <v>9.505867333268332</v>
       </c>
       <c r="N6" t="n">
-        <v>139.7571228419286</v>
+        <v>139.1169132564223</v>
       </c>
       <c r="O6" t="n">
-        <v>11.82189167781234</v>
+        <v>11.79478330688709</v>
       </c>
       <c r="P6" t="n">
-        <v>365.9087111891496</v>
+        <v>365.8961737932098</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -23247,28 +23350,28 @@
         <v>0.0435</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.07517322947316427</v>
+        <v>-0.07526682711900079</v>
       </c>
       <c r="J7" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K7" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00331743421819497</v>
+        <v>0.003358339507617658</v>
       </c>
       <c r="M7" t="n">
-        <v>7.843656803591482</v>
+        <v>7.807880931957675</v>
       </c>
       <c r="N7" t="n">
-        <v>104.7356845744683</v>
+        <v>104.250852262021</v>
       </c>
       <c r="O7" t="n">
-        <v>10.23404536703196</v>
+        <v>10.2103306636965</v>
       </c>
       <c r="P7" t="n">
-        <v>363.5417891042437</v>
+        <v>363.5427321416726</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -23325,28 +23428,28 @@
         <v>0.041</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02141659642383405</v>
+        <v>0.02073367638665826</v>
       </c>
       <c r="J8" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K8" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0003644221468016573</v>
+        <v>0.0003449117595434315</v>
       </c>
       <c r="M8" t="n">
-        <v>7.031536174508512</v>
+        <v>7.002134624045308</v>
       </c>
       <c r="N8" t="n">
-        <v>77.61605517725502</v>
+        <v>77.2596557812212</v>
       </c>
       <c r="O8" t="n">
-        <v>8.809997456143504</v>
+        <v>8.789747196661642</v>
       </c>
       <c r="P8" t="n">
-        <v>359.6320415368708</v>
+        <v>359.6389222564682</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -23403,28 +23506,28 @@
         <v>0.0357</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2611058468289939</v>
+        <v>-0.25930591259997</v>
       </c>
       <c r="J9" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K9" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03472827958573055</v>
+        <v>0.03458769522392224</v>
       </c>
       <c r="M9" t="n">
-        <v>9.029430697353686</v>
+        <v>8.996813444184333</v>
       </c>
       <c r="N9" t="n">
-        <v>116.899653880914</v>
+        <v>116.3788345025404</v>
       </c>
       <c r="O9" t="n">
-        <v>10.81201433040643</v>
+        <v>10.78790222900358</v>
       </c>
       <c r="P9" t="n">
-        <v>358.0867905900064</v>
+        <v>358.0686554613686</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -23481,28 +23584,28 @@
         <v>0.0255</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1660747472795427</v>
+        <v>-0.1590805057608667</v>
       </c>
       <c r="J10" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K10" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L10" t="n">
-        <v>0.008718044720948059</v>
+        <v>0.008070406982369493</v>
       </c>
       <c r="M10" t="n">
-        <v>10.92615676563149</v>
+        <v>10.91248933434688</v>
       </c>
       <c r="N10" t="n">
-        <v>193.4634937659018</v>
+        <v>192.8756022026719</v>
       </c>
       <c r="O10" t="n">
-        <v>13.90911549186007</v>
+        <v>13.88796609308476</v>
       </c>
       <c r="P10" t="n">
-        <v>346.6995823561588</v>
+        <v>346.6291122980753</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -23559,28 +23662,28 @@
         <v>0.0232</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2872411898121419</v>
+        <v>-0.2786228702011078</v>
       </c>
       <c r="J11" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K11" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L11" t="n">
-        <v>0.02050297654681954</v>
+        <v>0.01946431536524651</v>
       </c>
       <c r="M11" t="n">
-        <v>12.49768009230198</v>
+        <v>12.48836232905925</v>
       </c>
       <c r="N11" t="n">
-        <v>243.1606846457792</v>
+        <v>242.502238949023</v>
       </c>
       <c r="O11" t="n">
-        <v>15.59361037879872</v>
+        <v>15.57248339055216</v>
       </c>
       <c r="P11" t="n">
-        <v>343.0242292714098</v>
+        <v>342.9373959125745</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -23637,28 +23740,28 @@
         <v>0.031</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.3390271759176495</v>
+        <v>-0.3365762916677477</v>
       </c>
       <c r="J12" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K12" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L12" t="n">
-        <v>0.04473743923290263</v>
+        <v>0.04452621665945</v>
       </c>
       <c r="M12" t="n">
-        <v>10.07932624273981</v>
+        <v>10.04747098867248</v>
       </c>
       <c r="N12" t="n">
-        <v>151.4029639762769</v>
+        <v>150.7398158631195</v>
       </c>
       <c r="O12" t="n">
-        <v>12.30459117469072</v>
+        <v>12.27761442068937</v>
       </c>
       <c r="P12" t="n">
-        <v>345.6083133704341</v>
+        <v>345.5836196341676</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -23715,28 +23818,28 @@
         <v>0.036</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2556330724822458</v>
+        <v>-0.2469733574949573</v>
       </c>
       <c r="J13" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K13" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L13" t="n">
-        <v>0.02463209684879486</v>
+        <v>0.02318375680485008</v>
       </c>
       <c r="M13" t="n">
-        <v>9.99451236496061</v>
+        <v>9.999724064833265</v>
       </c>
       <c r="N13" t="n">
-        <v>159.6301325101529</v>
+        <v>159.3629021521399</v>
       </c>
       <c r="O13" t="n">
-        <v>12.63448188530709</v>
+        <v>12.62390201768613</v>
       </c>
       <c r="P13" t="n">
-        <v>344.259778539482</v>
+        <v>344.172528104033</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -23793,28 +23896,28 @@
         <v>0.0414</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2895137174823704</v>
+        <v>-0.2826769776776232</v>
       </c>
       <c r="J14" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K14" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0288521483992169</v>
+        <v>0.02776076851968678</v>
       </c>
       <c r="M14" t="n">
-        <v>10.63914992244555</v>
+        <v>10.62348140045486</v>
       </c>
       <c r="N14" t="n">
-        <v>174.0440601678796</v>
+        <v>173.5323681320609</v>
       </c>
       <c r="O14" t="n">
-        <v>13.19257594891459</v>
+        <v>13.1731684925101</v>
       </c>
       <c r="P14" t="n">
-        <v>338.7556507466601</v>
+        <v>338.6867675875848</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -23871,28 +23974,28 @@
         <v>0.042</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3102305093679493</v>
+        <v>-0.3019142897317797</v>
       </c>
       <c r="J15" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K15" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L15" t="n">
-        <v>0.02795989690715828</v>
+        <v>0.02671762283860035</v>
       </c>
       <c r="M15" t="n">
-        <v>11.69901082809663</v>
+        <v>11.67751102187474</v>
       </c>
       <c r="N15" t="n">
-        <v>206.9992977535439</v>
+        <v>206.4664529706704</v>
       </c>
       <c r="O15" t="n">
-        <v>14.38747016516607</v>
+        <v>14.36894056535382</v>
       </c>
       <c r="P15" t="n">
-        <v>336.0894381287795</v>
+        <v>336.0053462309168</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -23949,28 +24052,28 @@
         <v>0.0418</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2978610948017917</v>
+        <v>-0.2843893062852867</v>
       </c>
       <c r="J16" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K16" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L16" t="n">
-        <v>0.02266961329513451</v>
+        <v>0.02080521222467202</v>
       </c>
       <c r="M16" t="n">
-        <v>12.66728988786448</v>
+        <v>12.66480613875094</v>
       </c>
       <c r="N16" t="n">
-        <v>237.4895398808372</v>
+        <v>237.5278298413857</v>
       </c>
       <c r="O16" t="n">
-        <v>15.4106956326065</v>
+        <v>15.41193790025724</v>
       </c>
       <c r="P16" t="n">
-        <v>331.8891135434303</v>
+        <v>331.7530286919705</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -24027,28 +24130,28 @@
         <v>0.0382</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.4450432221377131</v>
+        <v>-0.4404523062617549</v>
       </c>
       <c r="J17" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K17" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L17" t="n">
-        <v>0.09232534921920132</v>
+        <v>0.09132489552608913</v>
       </c>
       <c r="M17" t="n">
-        <v>8.521851580856694</v>
+        <v>8.501737282918434</v>
       </c>
       <c r="N17" t="n">
-        <v>120.0159666545293</v>
+        <v>119.5818188257991</v>
       </c>
       <c r="O17" t="n">
-        <v>10.95517990060087</v>
+        <v>10.93534722017546</v>
       </c>
       <c r="P17" t="n">
-        <v>340.7069406578555</v>
+        <v>340.6604459660405</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -24105,28 +24208,28 @@
         <v>0.0385</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.7361316309003275</v>
+        <v>-0.7319777616312472</v>
       </c>
       <c r="J18" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K18" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1626990403415314</v>
+        <v>0.1624293341939634</v>
       </c>
       <c r="M18" t="n">
-        <v>9.629942815667373</v>
+        <v>9.606118394945462</v>
       </c>
       <c r="N18" t="n">
-        <v>167.8838416054521</v>
+        <v>167.1924923065941</v>
       </c>
       <c r="O18" t="n">
-        <v>12.95699971465046</v>
+        <v>12.93029358934259</v>
       </c>
       <c r="P18" t="n">
-        <v>341.4145702378786</v>
+        <v>341.3717705904764</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -24183,28 +24286,28 @@
         <v>0.0322</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.6786007088873214</v>
+        <v>-0.6713414513322857</v>
       </c>
       <c r="J19" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K19" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1152639139634135</v>
+        <v>0.1139350439664569</v>
       </c>
       <c r="M19" t="n">
-        <v>11.26429296619805</v>
+        <v>11.25289728299989</v>
       </c>
       <c r="N19" t="n">
-        <v>214.6752860481217</v>
+        <v>213.9853016205141</v>
       </c>
       <c r="O19" t="n">
-        <v>14.65180146084848</v>
+        <v>14.62823644943279</v>
       </c>
       <c r="P19" t="n">
-        <v>340.063798663333</v>
+        <v>339.9895539719105</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -24261,28 +24364,28 @@
         <v>0.0311</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.651326452429705</v>
+        <v>-0.6429637963851271</v>
       </c>
       <c r="J20" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K20" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1227626659866919</v>
+        <v>0.1208054172712335</v>
       </c>
       <c r="M20" t="n">
-        <v>10.92049882619608</v>
+        <v>10.91807782239032</v>
       </c>
       <c r="N20" t="n">
-        <v>186.4217945157786</v>
+        <v>185.9857668639982</v>
       </c>
       <c r="O20" t="n">
-        <v>13.65363667730245</v>
+        <v>13.63765987491982</v>
       </c>
       <c r="P20" t="n">
-        <v>344.5310905827832</v>
+        <v>344.4465801874543</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -24339,28 +24442,28 @@
         <v>0.0339</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.550559863603156</v>
+        <v>-0.543676757524592</v>
       </c>
       <c r="J21" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K21" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1139882193877415</v>
+        <v>0.1122478663552763</v>
       </c>
       <c r="M21" t="n">
-        <v>9.698317843271216</v>
+        <v>9.693566040823484</v>
       </c>
       <c r="N21" t="n">
-        <v>146.093620342484</v>
+        <v>145.7089285057632</v>
       </c>
       <c r="O21" t="n">
-        <v>12.08691939008795</v>
+        <v>12.07099534030907</v>
       </c>
       <c r="P21" t="n">
-        <v>343.3030684248171</v>
+        <v>343.2339346690905</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -24417,28 +24520,28 @@
         <v>0.038</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.6501934232901585</v>
+        <v>-0.641933292541957</v>
       </c>
       <c r="J22" t="n">
+        <v>216</v>
+      </c>
+      <c r="K22" t="n">
         <v>215</v>
       </c>
-      <c r="K22" t="n">
-        <v>214</v>
-      </c>
       <c r="L22" t="n">
-        <v>0.1490949506094421</v>
+        <v>0.1467555473853027</v>
       </c>
       <c r="M22" t="n">
-        <v>9.628027456881867</v>
+        <v>9.625897688393044</v>
       </c>
       <c r="N22" t="n">
-        <v>149.1289543116255</v>
+        <v>148.8622087699197</v>
       </c>
       <c r="O22" t="n">
-        <v>12.2118366477621</v>
+        <v>12.20091016153794</v>
       </c>
       <c r="P22" t="n">
-        <v>343.9505576934719</v>
+        <v>343.8675423803439</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -24495,28 +24598,28 @@
         <v>0.052</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.7667889229943277</v>
+        <v>-0.7679904029325755</v>
       </c>
       <c r="J23" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K23" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1897940089853503</v>
+        <v>0.1917917762590592</v>
       </c>
       <c r="M23" t="n">
-        <v>9.943441796729804</v>
+        <v>9.903452765921461</v>
       </c>
       <c r="N23" t="n">
-        <v>155.8013131270703</v>
+        <v>155.0823532785013</v>
       </c>
       <c r="O23" t="n">
-        <v>12.4820396220758</v>
+        <v>12.45320654604674</v>
       </c>
       <c r="P23" t="n">
-        <v>340.3069326174346</v>
+        <v>340.3189871665755</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -24573,28 +24676,28 @@
         <v>0.0404</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.4028038650970511</v>
+        <v>-0.404484454529403</v>
       </c>
       <c r="J24" t="n">
+        <v>216</v>
+      </c>
+      <c r="K24" t="n">
         <v>215</v>
       </c>
-      <c r="K24" t="n">
-        <v>214</v>
-      </c>
       <c r="L24" t="n">
-        <v>0.0596589526251573</v>
+        <v>0.06068231018440129</v>
       </c>
       <c r="M24" t="n">
-        <v>9.987541366452673</v>
+        <v>9.950239475444683</v>
       </c>
       <c r="N24" t="n">
-        <v>158.0722701936876</v>
+        <v>157.3547209886013</v>
       </c>
       <c r="O24" t="n">
-        <v>12.57267951526991</v>
+        <v>12.54411100830192</v>
       </c>
       <c r="P24" t="n">
-        <v>340.5696062576222</v>
+        <v>340.586496384694</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -24651,28 +24754,28 @@
         <v>0.0364</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1935278301883103</v>
+        <v>-0.1912182559533317</v>
       </c>
       <c r="J25" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K25" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L25" t="n">
-        <v>0.02813836371283596</v>
+        <v>0.02774362307210698</v>
       </c>
       <c r="M25" t="n">
-        <v>6.755854247568617</v>
+        <v>6.734625261229369</v>
       </c>
       <c r="N25" t="n">
-        <v>80.6244533559107</v>
+        <v>80.27953681802235</v>
       </c>
       <c r="O25" t="n">
-        <v>8.979112058322398</v>
+        <v>8.959884866337422</v>
       </c>
       <c r="P25" t="n">
-        <v>355.7795840342011</v>
+        <v>355.7564794430141</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -24729,28 +24832,28 @@
         <v>0.0501</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4064906064320072</v>
+        <v>-0.3980457636083921</v>
       </c>
       <c r="J26" t="n">
+        <v>216</v>
+      </c>
+      <c r="K26" t="n">
         <v>215</v>
       </c>
-      <c r="K26" t="n">
-        <v>214</v>
-      </c>
       <c r="L26" t="n">
-        <v>0.1048505919015186</v>
+        <v>0.1014070332244745</v>
       </c>
       <c r="M26" t="n">
-        <v>7.540071346562805</v>
+        <v>7.548000943495919</v>
       </c>
       <c r="N26" t="n">
-        <v>87.19354458749375</v>
+        <v>87.23417574993222</v>
       </c>
       <c r="O26" t="n">
-        <v>9.337748368182437</v>
+        <v>9.339923755038486</v>
       </c>
       <c r="P26" t="n">
-        <v>338.9779717810367</v>
+        <v>338.8931000892087</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -24807,28 +24910,28 @@
         <v>0.031</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.8055887730997489</v>
+        <v>-0.7820246578369083</v>
       </c>
       <c r="J27" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K27" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L27" t="n">
-        <v>0.1099495986324776</v>
+        <v>0.1042123273071995</v>
       </c>
       <c r="M27" t="n">
-        <v>13.07726129688534</v>
+        <v>13.0972774449483</v>
       </c>
       <c r="N27" t="n">
-        <v>323.696387815509</v>
+        <v>325.6117076110133</v>
       </c>
       <c r="O27" t="n">
-        <v>17.99156435153733</v>
+        <v>18.04471411829551</v>
       </c>
       <c r="P27" t="n">
-        <v>324.8444582374207</v>
+        <v>324.6069260628388</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -24885,28 +24988,28 @@
         <v>0.0477</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.3644927769154966</v>
+        <v>-0.3452584184203517</v>
       </c>
       <c r="J28" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K28" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L28" t="n">
-        <v>0.02135076655527202</v>
+        <v>0.01926996654580093</v>
       </c>
       <c r="M28" t="n">
-        <v>14.55639408833556</v>
+        <v>14.57276612545875</v>
       </c>
       <c r="N28" t="n">
-        <v>373.1300600553971</v>
+        <v>373.6751957921761</v>
       </c>
       <c r="O28" t="n">
-        <v>19.3165747495615</v>
+        <v>19.3306801688967</v>
       </c>
       <c r="P28" t="n">
-        <v>331.3563898632346</v>
+        <v>331.1615454423662</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -24944,7 +25047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC216"/>
+  <dimension ref="A1:AC217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56503,6 +56606,153 @@
         </is>
       </c>
     </row>
+    <row r="217">
+      <c r="A217" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:17:49+00:00</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>-35.268109002107074,173.13703075747517</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>-35.2674224765075,173.13663489567733</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>-35.26680361661442,173.13614048694782</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>-35.26622660468569,173.13558512985142</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>-35.2656409061486,173.13504241728185</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>-35.26504889440538,173.13450889287628</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>-35.26447488126269,173.1339491516866</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>-35.26387632114648,173.13342515223772</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>-35.26329807492344,173.1328715642889</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>-35.26270651152594,173.13233736427068</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>-35.262109040283065,173.1318117620721</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>-35.261593992095555,173.1311661227533</t>
+        </is>
+      </c>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>-35.26098198451319,173.1306616783323</t>
+        </is>
+      </c>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>-35.26041078123638,173.1300978055031</t>
+        </is>
+      </c>
+      <c r="P217" t="inlineStr">
+        <is>
+          <t>-35.25986093301273,173.12950282792033</t>
+        </is>
+      </c>
+      <c r="Q217" t="inlineStr">
+        <is>
+          <t>-35.25926604788308,173.12897343131652</t>
+        </is>
+      </c>
+      <c r="R217" t="inlineStr">
+        <is>
+          <t>-35.25865877222091,173.12846207317756</t>
+        </is>
+      </c>
+      <c r="S217" t="inlineStr">
+        <is>
+          <t>-35.25811834725489,173.12785335565172</t>
+        </is>
+      </c>
+      <c r="T217" t="inlineStr">
+        <is>
+          <t>-35.25759400941593,173.12722120484432</t>
+        </is>
+      </c>
+      <c r="U217" t="inlineStr">
+        <is>
+          <t>-35.25703042341331,173.1266462049967</t>
+        </is>
+      </c>
+      <c r="V217" t="inlineStr">
+        <is>
+          <t>-35.256465444358,173.12607322815853</t>
+        </is>
+      </c>
+      <c r="W217" t="inlineStr">
+        <is>
+          <t>-35.25579968987013,173.12564700390135</t>
+        </is>
+      </c>
+      <c r="X217" t="inlineStr">
+        <is>
+          <t>-35.25529217951238,173.12499032472414</t>
+        </is>
+      </c>
+      <c r="Y217" t="inlineStr">
+        <is>
+          <t>-35.25487727399132,173.12419877927013</t>
+        </is>
+      </c>
+      <c r="Z217" t="inlineStr">
+        <is>
+          <t>-35.25422586329149,173.12375164999438</t>
+        </is>
+      </c>
+      <c r="AA217" t="inlineStr">
+        <is>
+          <t>-35.25362000120885,173.12323818255342</t>
+        </is>
+      </c>
+      <c r="AB217" t="inlineStr">
+        <is>
+          <t>-35.25313522074701,173.12254837854735</t>
+        </is>
+      </c>
+      <c r="AC217" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
